--- a/purchase_order_generator/templates/thd_template_clean.xlsx
+++ b/purchase_order_generator/templates/thd_template_clean.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="46">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -127,12 +127,6 @@
     <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="24"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
       <b val="1"/>
       <color rgb="FFFF0000"/>
       <sz val="14"/>
@@ -356,13 +350,6 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="24"/>
-      <vertAlign val="superscript"/>
-    </font>
   </fonts>
   <fills count="39">
     <fill>
@@ -594,7 +581,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -687,37 +674,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,6 +766,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -830,11 +800,13 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -955,146 +927,146 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="21" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="23" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="10" borderId="24" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="23" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="25" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="22" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="23" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="22" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="24" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="25" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="26" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="27" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="36" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="37" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="38" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="37" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="38" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1143,13 +1115,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
@@ -1158,29 +1124,14 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="50">
       <alignment horizontal="center" vertical="center"/>
@@ -1191,25 +1142,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="50">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
@@ -1218,141 +1160,92 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="50">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="50">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="50">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="50">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="50">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1980,7 +1873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U49"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="36.9583333333333" customWidth="1" style="17" min="1" max="1"/>
@@ -1991,7 +1884,7 @@
     <col width="10" customWidth="1" style="17" min="9" max="9"/>
     <col width="11.125" customWidth="1" style="17" min="10" max="10"/>
     <col width="12.625" customWidth="1" style="17" min="11" max="11"/>
-    <col width="30.8916666666667" customWidth="1" style="83" min="12" max="12"/>
+    <col width="30.8916666666667" customWidth="1" style="1" min="12" max="12"/>
     <col width="11.425" customWidth="1" style="17" min="13" max="13"/>
     <col width="19.1083333333333" customWidth="1" style="17" min="14" max="14"/>
     <col width="18.2083333333333" customWidth="1" style="17" min="15" max="16"/>
@@ -2000,8 +1893,8 @@
     <col width="9" customWidth="1" style="17" min="22" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="83">
-      <c r="A1" s="73" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="1">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>生产订单</t>
         </is>
@@ -2021,23 +1914,23 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="4" t="n"/>
     </row>
-    <row r="2" ht="25" customHeight="1" s="83">
-      <c r="A2" s="21" t="inlineStr">
+    <row r="2" ht="25" customHeight="1" s="1">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>款号</t>
         </is>
       </c>
-      <c r="B2" s="22" t="n"/>
+      <c r="B2" s="20" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="4" t="n"/>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="H2" s="22" t="n"/>
+      <c r="H2" s="20" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
@@ -2046,23 +1939,23 @@
       <c r="N2" s="3" t="n"/>
       <c r="O2" s="4" t="n"/>
     </row>
-    <row r="3" ht="25" customHeight="1" s="83">
-      <c r="A3" s="21" t="inlineStr">
+    <row r="3" ht="25" customHeight="1" s="1">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>订单号</t>
         </is>
       </c>
-      <c r="B3" s="26" t="n"/>
+      <c r="B3" s="21" t="n"/>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="27" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t>品牌</t>
         </is>
       </c>
-      <c r="H3" s="98" t="n"/>
+      <c r="H3" s="23" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
@@ -2071,23 +1964,23 @@
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="4" t="n"/>
     </row>
-    <row r="4" ht="25" customHeight="1" s="83">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="4" ht="25" customHeight="1" s="1">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>做货纸样编号</t>
         </is>
       </c>
-      <c r="B4" s="26" t="n"/>
+      <c r="B4" s="21" t="n"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="34" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>店铺</t>
         </is>
       </c>
-      <c r="H4" s="98" t="n"/>
+      <c r="H4" s="23" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
@@ -2095,30 +1988,30 @@
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="4" t="n"/>
-      <c r="P4" s="33" t="n"/>
-      <c r="Q4" s="33" t="n"/>
-      <c r="R4" s="33" t="n"/>
-      <c r="S4" s="33" t="n"/>
-      <c r="T4" s="33" t="n"/>
-      <c r="U4" s="33" t="n"/>
-    </row>
-    <row r="5" ht="25" customHeight="1" s="83">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="P4" s="26" t="n"/>
+      <c r="Q4" s="26" t="n"/>
+      <c r="R4" s="26" t="n"/>
+      <c r="S4" s="26" t="n"/>
+      <c r="T4" s="26" t="n"/>
+      <c r="U4" s="26" t="n"/>
+    </row>
+    <row r="5" ht="25" customHeight="1" s="1">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>加工厂</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n"/>
+      <c r="B5" s="21" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="34" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="H5" s="98" t="n"/>
+      <c r="H5" s="23" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
@@ -2126,417 +2019,622 @@
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="4" t="n"/>
-      <c r="P5" s="36" t="n"/>
-      <c r="Q5" s="36" t="n"/>
-      <c r="R5" s="36" t="n"/>
-      <c r="S5" s="36" t="n"/>
-      <c r="T5" s="36" t="n"/>
-      <c r="U5" s="36" t="n"/>
-    </row>
-    <row r="6" ht="25" customHeight="1" s="83">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>颜色尺码</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="P5" s="27" t="n"/>
+      <c r="Q5" s="27" t="n"/>
+      <c r="R5" s="27" t="n"/>
+      <c r="S5" s="27" t="n"/>
+      <c r="T5" s="27" t="n"/>
+      <c r="U5" s="27" t="n"/>
+    </row>
+    <row r="6" ht="25" customHeight="1" s="1">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                颜色
+尺码</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>包装袋规格</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D6" s="39" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E6" s="39" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F6" s="39" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="G6" s="39" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
       </c>
-      <c r="H6" s="39" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
       </c>
-      <c r="I6" s="39" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>4XL</t>
         </is>
       </c>
-      <c r="J6" s="39" t="inlineStr">
+      <c r="J6" s="29" t="inlineStr">
         <is>
           <t>5XL</t>
         </is>
       </c>
-      <c r="K6" s="39" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t>6XL</t>
         </is>
       </c>
-      <c r="L6" s="99" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>比例</t>
         </is>
       </c>
-      <c r="M6" s="99" t="inlineStr">
+      <c r="M6" s="30" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="N6" s="41" t="inlineStr">
+      <c r="N6" s="31" t="inlineStr">
         <is>
           <t>布料
 条数</t>
         </is>
       </c>
-      <c r="O6" s="42" t="inlineStr">
+      <c r="O6" s="32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="25" customHeight="1" s="83">
-      <c r="A7" s="97" t="n"/>
-      <c r="B7" s="97" t="n"/>
-      <c r="C7" s="97" t="n"/>
-      <c r="D7" s="97" t="n"/>
-      <c r="E7" s="97" t="n"/>
-      <c r="F7" s="97" t="n"/>
-      <c r="G7" s="97" t="n"/>
-      <c r="H7" s="97" t="n"/>
-      <c r="I7" s="97" t="n"/>
-      <c r="J7" s="97" t="n"/>
-      <c r="K7" s="97" t="n"/>
-      <c r="L7" s="97" t="n"/>
-      <c r="M7" s="97" t="n"/>
-      <c r="N7" s="97" t="n"/>
-      <c r="O7" s="97" t="n"/>
-    </row>
-    <row r="8" ht="25" customHeight="1" s="83">
-      <c r="A8" s="47" t="n"/>
-      <c r="B8" s="48" t="n"/>
-      <c r="C8" s="47" t="n"/>
-      <c r="D8" s="47" t="n"/>
-      <c r="E8" s="47" t="n"/>
-      <c r="F8" s="47" t="n"/>
-      <c r="G8" s="47" t="n"/>
-      <c r="H8" s="47" t="n"/>
-      <c r="I8" s="47" t="n"/>
-      <c r="J8" s="47" t="n"/>
-      <c r="K8" s="47" t="n"/>
-      <c r="L8" s="48" t="n"/>
-      <c r="M8" s="49" t="n"/>
-      <c r="N8" s="49" t="n"/>
-      <c r="O8" s="50" t="n"/>
-    </row>
-    <row r="9" ht="25" customHeight="1" s="83">
-      <c r="A9" s="51" t="n"/>
-      <c r="B9" s="48" t="n"/>
-      <c r="C9" s="47" t="n"/>
-      <c r="D9" s="47" t="n"/>
-      <c r="E9" s="47" t="n"/>
-      <c r="F9" s="47" t="n"/>
-      <c r="G9" s="47" t="n"/>
-      <c r="H9" s="47" t="n"/>
-      <c r="I9" s="47" t="n"/>
-      <c r="J9" s="47" t="n"/>
-      <c r="K9" s="47" t="n"/>
-      <c r="L9" s="48" t="n"/>
-      <c r="M9" s="52" t="n"/>
-      <c r="N9" s="52" t="n"/>
-      <c r="O9" s="53" t="n"/>
-    </row>
-    <row r="10" ht="25" customHeight="1" s="83">
-      <c r="A10" s="47" t="n"/>
-      <c r="B10" s="48" t="n"/>
-      <c r="C10" s="47" t="n"/>
-      <c r="D10" s="47" t="n"/>
-      <c r="E10" s="47" t="n"/>
-      <c r="F10" s="47" t="n"/>
-      <c r="G10" s="47" t="n"/>
-      <c r="H10" s="47" t="n"/>
-      <c r="I10" s="47" t="n"/>
-      <c r="J10" s="47" t="n"/>
-      <c r="K10" s="47" t="n"/>
-      <c r="L10" s="48" t="n"/>
-      <c r="M10" s="52" t="n"/>
-      <c r="N10" s="52" t="n"/>
-      <c r="O10" s="53" t="n"/>
-    </row>
-    <row r="11" ht="25" customHeight="1" s="83">
-      <c r="A11" s="54" t="n"/>
-      <c r="B11" s="48" t="n"/>
-      <c r="C11" s="47" t="n"/>
-      <c r="D11" s="47" t="n"/>
-      <c r="E11" s="47" t="n"/>
-      <c r="F11" s="47" t="n"/>
-      <c r="G11" s="47" t="n"/>
-      <c r="H11" s="47" t="n"/>
-      <c r="I11" s="47" t="n"/>
-      <c r="J11" s="47" t="n"/>
-      <c r="K11" s="47" t="n"/>
-      <c r="L11" s="48" t="n"/>
-      <c r="M11" s="52" t="n"/>
-      <c r="N11" s="52" t="n"/>
-      <c r="O11" s="53" t="n"/>
-    </row>
-    <row r="12" ht="25" customHeight="1" s="83">
-      <c r="A12" s="55" t="n"/>
-      <c r="B12" s="48" t="n"/>
-      <c r="C12" s="47" t="n"/>
-      <c r="D12" s="47" t="n"/>
-      <c r="E12" s="47" t="n"/>
-      <c r="F12" s="47" t="n"/>
-      <c r="G12" s="47" t="n"/>
-      <c r="H12" s="47" t="n"/>
-      <c r="I12" s="47" t="n"/>
-      <c r="J12" s="47" t="n"/>
-      <c r="K12" s="47" t="n"/>
-      <c r="L12" s="48" t="n"/>
-      <c r="M12" s="52" t="n"/>
-      <c r="N12" s="52" t="n"/>
-      <c r="O12" s="53" t="n"/>
-    </row>
-    <row r="13" ht="25" customHeight="1" s="83">
-      <c r="A13" s="55" t="n"/>
-      <c r="B13" s="48" t="n"/>
-      <c r="C13" s="47" t="n"/>
-      <c r="D13" s="47" t="n"/>
-      <c r="E13" s="47" t="n"/>
-      <c r="F13" s="47" t="n"/>
-      <c r="G13" s="47" t="n"/>
-      <c r="H13" s="47" t="n"/>
-      <c r="I13" s="47" t="n"/>
-      <c r="J13" s="47" t="n"/>
-      <c r="K13" s="47" t="n"/>
-      <c r="L13" s="48" t="n"/>
-      <c r="M13" s="52" t="n"/>
-      <c r="N13" s="52" t="n"/>
-      <c r="O13" s="53" t="n"/>
-    </row>
-    <row r="14" ht="25" customHeight="1" s="83">
-      <c r="A14" s="55" t="n"/>
-      <c r="B14" s="48" t="n"/>
-      <c r="C14" s="47" t="n"/>
-      <c r="D14" s="47" t="n"/>
-      <c r="E14" s="47" t="n"/>
-      <c r="F14" s="47" t="n"/>
-      <c r="G14" s="47" t="n"/>
-      <c r="H14" s="47" t="n"/>
-      <c r="I14" s="47" t="n"/>
-      <c r="J14" s="47" t="n"/>
-      <c r="K14" s="47" t="n"/>
-      <c r="L14" s="48" t="n"/>
-      <c r="M14" s="52" t="n"/>
-      <c r="N14" s="52" t="n"/>
-      <c r="O14" s="53" t="n"/>
-    </row>
-    <row r="15" ht="25" customHeight="1" s="83">
-      <c r="A15" s="55" t="n"/>
-      <c r="B15" s="48" t="n"/>
-      <c r="C15" s="47" t="n"/>
-      <c r="D15" s="47" t="n"/>
-      <c r="E15" s="47" t="n"/>
-      <c r="F15" s="47" t="n"/>
-      <c r="G15" s="47" t="n"/>
-      <c r="H15" s="47" t="n"/>
-      <c r="I15" s="47" t="n"/>
-      <c r="J15" s="47" t="n"/>
-      <c r="K15" s="47" t="n"/>
-      <c r="L15" s="48" t="n"/>
-      <c r="M15" s="52" t="n"/>
-      <c r="N15" s="52" t="n"/>
-      <c r="O15" s="53" t="n"/>
-    </row>
-    <row r="16" ht="25" customHeight="1" s="83">
-      <c r="A16" s="55" t="n"/>
-      <c r="B16" s="48" t="n"/>
-      <c r="C16" s="47" t="n"/>
-      <c r="D16" s="47" t="n"/>
-      <c r="E16" s="47" t="n"/>
-      <c r="F16" s="47" t="n"/>
-      <c r="G16" s="47" t="n"/>
-      <c r="H16" s="47" t="n"/>
-      <c r="I16" s="47" t="n"/>
-      <c r="J16" s="47" t="n"/>
-      <c r="K16" s="47" t="n"/>
-      <c r="L16" s="48" t="n"/>
-      <c r="M16" s="52" t="n"/>
-      <c r="N16" s="52" t="n"/>
-      <c r="O16" s="53" t="n"/>
-    </row>
-    <row r="17" ht="25" customHeight="1" s="83">
-      <c r="A17" s="55" t="n"/>
-      <c r="B17" s="48" t="n"/>
-      <c r="C17" s="47" t="n"/>
-      <c r="D17" s="47" t="n"/>
-      <c r="E17" s="47" t="n"/>
-      <c r="F17" s="47" t="n"/>
-      <c r="G17" s="47" t="n"/>
-      <c r="H17" s="47" t="n"/>
-      <c r="I17" s="47" t="n"/>
-      <c r="J17" s="47" t="n"/>
-      <c r="K17" s="47" t="n"/>
-      <c r="L17" s="48" t="n"/>
-      <c r="M17" s="52" t="n"/>
-      <c r="N17" s="52" t="n"/>
-      <c r="O17" s="53" t="n"/>
-    </row>
-    <row r="18" ht="25" customHeight="1" s="83">
-      <c r="A18" s="55" t="n"/>
-      <c r="B18" s="48" t="n"/>
-      <c r="C18" s="47" t="n"/>
-      <c r="D18" s="47" t="n"/>
-      <c r="E18" s="47" t="n"/>
-      <c r="F18" s="47" t="n"/>
-      <c r="G18" s="47" t="n"/>
-      <c r="H18" s="47" t="n"/>
-      <c r="I18" s="47" t="n"/>
-      <c r="J18" s="47" t="n"/>
-      <c r="K18" s="47" t="n"/>
-      <c r="L18" s="48" t="n"/>
-      <c r="M18" s="52" t="n"/>
-      <c r="N18" s="52" t="n"/>
-      <c r="O18" s="53" t="n"/>
-    </row>
-    <row r="19" ht="25" customHeight="1" s="83">
-      <c r="A19" s="55" t="n"/>
-      <c r="B19" s="48" t="n"/>
-      <c r="C19" s="47" t="n"/>
-      <c r="D19" s="47" t="n"/>
-      <c r="E19" s="47" t="n"/>
-      <c r="F19" s="47" t="n"/>
-      <c r="G19" s="47" t="n"/>
-      <c r="H19" s="47" t="n"/>
-      <c r="I19" s="47" t="n"/>
-      <c r="J19" s="47" t="n"/>
-      <c r="K19" s="47" t="n"/>
-      <c r="L19" s="48" t="n"/>
-      <c r="M19" s="52" t="n"/>
-      <c r="N19" s="52" t="n"/>
-      <c r="O19" s="53" t="n"/>
-    </row>
-    <row r="20" ht="25" customHeight="1" s="83">
-      <c r="A20" s="55" t="n"/>
-      <c r="B20" s="48" t="n"/>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="47" t="n"/>
-      <c r="E20" s="47" t="n"/>
-      <c r="F20" s="47" t="n"/>
-      <c r="G20" s="47" t="n"/>
-      <c r="H20" s="47" t="n"/>
-      <c r="I20" s="47" t="n"/>
-      <c r="J20" s="47" t="n"/>
-      <c r="K20" s="47" t="n"/>
-      <c r="L20" s="48" t="n"/>
-      <c r="M20" s="52" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="O20" s="53" t="n"/>
-    </row>
-    <row r="21" ht="25" customHeight="1" s="83">
-      <c r="A21" s="55" t="n"/>
-      <c r="B21" s="48" t="n"/>
-      <c r="C21" s="47" t="n"/>
-      <c r="D21" s="47" t="n"/>
-      <c r="E21" s="47" t="n"/>
-      <c r="F21" s="47" t="n"/>
-      <c r="G21" s="47" t="n"/>
-      <c r="H21" s="47" t="n"/>
-      <c r="I21" s="47" t="n"/>
-      <c r="J21" s="47" t="n"/>
-      <c r="K21" s="47" t="n"/>
-      <c r="L21" s="48" t="n"/>
-      <c r="M21" s="52" t="n"/>
-      <c r="N21" s="52" t="n"/>
-      <c r="O21" s="53" t="n"/>
-    </row>
-    <row r="22" ht="25" customHeight="1" s="83">
-      <c r="A22" s="55" t="n"/>
-      <c r="B22" s="48" t="n"/>
-      <c r="C22" s="47" t="n"/>
-      <c r="D22" s="47" t="n"/>
-      <c r="E22" s="47" t="n"/>
-      <c r="F22" s="47" t="n"/>
-      <c r="G22" s="47" t="n"/>
-      <c r="H22" s="47" t="n"/>
-      <c r="I22" s="47" t="n"/>
-      <c r="J22" s="47" t="n"/>
-      <c r="K22" s="47" t="n"/>
-      <c r="L22" s="48" t="n"/>
-      <c r="M22" s="52" t="n"/>
-      <c r="N22" s="52" t="n"/>
-      <c r="O22" s="53" t="n"/>
-    </row>
-    <row r="23" ht="25" customHeight="1" s="83">
-      <c r="A23" s="55" t="n"/>
-      <c r="B23" s="48" t="n"/>
-      <c r="C23" s="47" t="n"/>
-      <c r="D23" s="47" t="n"/>
-      <c r="E23" s="47" t="n"/>
-      <c r="F23" s="47" t="n"/>
-      <c r="G23" s="47" t="n"/>
-      <c r="H23" s="47" t="n"/>
-      <c r="I23" s="47" t="n"/>
-      <c r="J23" s="47" t="n"/>
-      <c r="K23" s="47" t="n"/>
-      <c r="L23" s="48" t="n"/>
-      <c r="M23" s="52" t="n"/>
-      <c r="N23" s="52" t="n"/>
-      <c r="O23" s="53" t="n"/>
-    </row>
-    <row r="24" ht="30" customHeight="1" s="83">
-      <c r="A24" s="56" t="inlineStr">
+    <row r="7" ht="68" customHeight="1" s="1">
+      <c r="A7" s="34" t="n"/>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="34" t="n"/>
+      <c r="O7" s="34" t="n"/>
+    </row>
+    <row r="8" ht="25" customHeight="1" s="1">
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="35" t="n"/>
+      <c r="H8" s="35" t="n"/>
+      <c r="I8" s="35" t="n"/>
+      <c r="J8" s="35" t="n"/>
+      <c r="K8" s="35" t="n"/>
+      <c r="L8" s="36" t="n"/>
+      <c r="M8" s="37" t="n"/>
+      <c r="N8" s="37" t="n"/>
+      <c r="O8" s="38" t="n"/>
+    </row>
+    <row r="9" ht="25" customHeight="1" s="1">
+      <c r="A9" s="39" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
+      <c r="I9" s="35" t="n"/>
+      <c r="J9" s="35" t="n"/>
+      <c r="K9" s="35" t="n"/>
+      <c r="L9" s="36" t="n"/>
+      <c r="M9" s="40" t="n"/>
+      <c r="N9" s="40" t="n"/>
+      <c r="O9" s="41" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1" s="1">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="35" t="n"/>
+      <c r="I10" s="35" t="n"/>
+      <c r="J10" s="35" t="n"/>
+      <c r="K10" s="35" t="n"/>
+      <c r="L10" s="36" t="n"/>
+      <c r="M10" s="40" t="n"/>
+      <c r="N10" s="40" t="n"/>
+      <c r="O10" s="41" t="n"/>
+    </row>
+    <row r="11" ht="25" customHeight="1" s="1">
+      <c r="A11" s="42" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="35" t="n"/>
+      <c r="K11" s="35" t="n"/>
+      <c r="L11" s="36" t="n"/>
+      <c r="M11" s="40" t="n"/>
+      <c r="N11" s="40" t="n"/>
+      <c r="O11" s="41" t="n"/>
+    </row>
+    <row r="12" ht="25" customHeight="1" s="1">
+      <c r="A12" s="43" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="35" t="n"/>
+      <c r="I12" s="35" t="n"/>
+      <c r="J12" s="35" t="n"/>
+      <c r="K12" s="35" t="n"/>
+      <c r="L12" s="36" t="n"/>
+      <c r="M12" s="40" t="n"/>
+      <c r="N12" s="40" t="n"/>
+      <c r="O12" s="41" t="n"/>
+    </row>
+    <row r="13" ht="25" customHeight="1" s="1">
+      <c r="A13" s="43" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="35" t="n"/>
+      <c r="I13" s="35" t="n"/>
+      <c r="J13" s="35" t="n"/>
+      <c r="K13" s="35" t="n"/>
+      <c r="L13" s="36" t="n"/>
+      <c r="M13" s="40" t="n"/>
+      <c r="N13" s="40" t="n"/>
+      <c r="O13" s="41" t="n"/>
+    </row>
+    <row r="14" ht="25" customHeight="1" s="1">
+      <c r="A14" s="43" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="35" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="35" t="n"/>
+      <c r="K14" s="35" t="n"/>
+      <c r="L14" s="36" t="n"/>
+      <c r="M14" s="40" t="n"/>
+      <c r="N14" s="40" t="n"/>
+      <c r="O14" s="41" t="n"/>
+    </row>
+    <row r="15" ht="25" customHeight="1" s="1">
+      <c r="A15" s="43" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="35" t="n"/>
+      <c r="I15" s="35" t="n"/>
+      <c r="J15" s="35" t="n"/>
+      <c r="K15" s="35" t="n"/>
+      <c r="L15" s="36" t="n"/>
+      <c r="M15" s="40" t="n"/>
+      <c r="N15" s="40" t="n"/>
+      <c r="O15" s="41" t="n"/>
+    </row>
+    <row r="16" ht="25" customHeight="1" s="1">
+      <c r="A16" s="43" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="35" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="35" t="n"/>
+      <c r="K16" s="35" t="n"/>
+      <c r="L16" s="36" t="n"/>
+      <c r="M16" s="40" t="n"/>
+      <c r="N16" s="40" t="n"/>
+      <c r="O16" s="41" t="n"/>
+    </row>
+    <row r="17" ht="25" customHeight="1" s="1">
+      <c r="A17" s="43" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="35" t="n"/>
+      <c r="I17" s="35" t="n"/>
+      <c r="J17" s="35" t="n"/>
+      <c r="K17" s="35" t="n"/>
+      <c r="L17" s="36" t="n"/>
+      <c r="M17" s="40" t="n"/>
+      <c r="N17" s="40" t="n"/>
+      <c r="O17" s="41" t="n"/>
+    </row>
+    <row r="18" ht="25" customHeight="1" s="1">
+      <c r="A18" s="43" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
+      <c r="H18" s="35" t="n"/>
+      <c r="I18" s="35" t="n"/>
+      <c r="J18" s="35" t="n"/>
+      <c r="K18" s="35" t="n"/>
+      <c r="L18" s="36" t="n"/>
+      <c r="M18" s="40" t="n"/>
+      <c r="N18" s="40" t="n"/>
+      <c r="O18" s="41" t="n"/>
+    </row>
+    <row r="19" ht="25" customHeight="1" s="1">
+      <c r="A19" s="43" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n"/>
+      <c r="I19" s="35" t="n"/>
+      <c r="J19" s="35" t="n"/>
+      <c r="K19" s="35" t="n"/>
+      <c r="L19" s="36" t="n"/>
+      <c r="M19" s="40" t="n"/>
+      <c r="N19" s="40" t="n"/>
+      <c r="O19" s="41" t="n"/>
+    </row>
+    <row r="20" ht="25" customHeight="1" s="1">
+      <c r="A20" s="43" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
+      <c r="H20" s="35" t="n"/>
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" s="35" t="n"/>
+      <c r="K20" s="35" t="n"/>
+      <c r="L20" s="36" t="n"/>
+      <c r="M20" s="40" t="n"/>
+      <c r="N20" s="40" t="n"/>
+      <c r="O20" s="41" t="n"/>
+    </row>
+    <row r="21" ht="25" customHeight="1" s="1">
+      <c r="A21" s="43" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="35" t="n"/>
+      <c r="J21" s="35" t="n"/>
+      <c r="K21" s="35" t="n"/>
+      <c r="L21" s="36" t="n"/>
+      <c r="M21" s="40" t="n"/>
+      <c r="N21" s="40" t="n"/>
+      <c r="O21" s="41" t="n"/>
+    </row>
+    <row r="22" ht="25" customHeight="1" s="1">
+      <c r="A22" s="43" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="35" t="n"/>
+      <c r="I22" s="35" t="n"/>
+      <c r="J22" s="35" t="n"/>
+      <c r="K22" s="35" t="n"/>
+      <c r="L22" s="36" t="n"/>
+      <c r="M22" s="40" t="n"/>
+      <c r="N22" s="40" t="n"/>
+      <c r="O22" s="41" t="n"/>
+    </row>
+    <row r="23" ht="25" customHeight="1" s="1">
+      <c r="A23" s="43" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="35" t="n"/>
+      <c r="I23" s="35" t="n"/>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="35" t="n"/>
+      <c r="L23" s="36" t="n"/>
+      <c r="M23" s="40" t="n"/>
+      <c r="N23" s="40" t="n"/>
+      <c r="O23" s="41" t="n"/>
+    </row>
+    <row r="24" ht="25" customHeight="1" s="1">
+      <c r="A24" s="35" t="n"/>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="35" t="n"/>
+      <c r="I24" s="35" t="n"/>
+      <c r="J24" s="35" t="n"/>
+      <c r="K24" s="35" t="n"/>
+      <c r="L24" s="36" t="n"/>
+      <c r="M24" s="44" t="n"/>
+      <c r="N24" s="44" t="n"/>
+      <c r="O24" s="45" t="n"/>
+    </row>
+    <row r="25" ht="25" customHeight="1" s="1">
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="35" t="n"/>
+      <c r="I25" s="35" t="n"/>
+      <c r="J25" s="35" t="n"/>
+      <c r="K25" s="35" t="n"/>
+      <c r="L25" s="36" t="n"/>
+      <c r="M25" s="44" t="n"/>
+      <c r="N25" s="44" t="n"/>
+      <c r="O25" s="45" t="n"/>
+    </row>
+    <row r="26" ht="25" customHeight="1" s="1">
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="35" t="n"/>
+      <c r="J26" s="35" t="n"/>
+      <c r="K26" s="35" t="n"/>
+      <c r="L26" s="36" t="n"/>
+      <c r="M26" s="44" t="n"/>
+      <c r="N26" s="44" t="n"/>
+      <c r="O26" s="45" t="n"/>
+    </row>
+    <row r="27" ht="25" customHeight="1" s="1">
+      <c r="A27" s="35" t="n"/>
+      <c r="B27" s="36" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="35" t="n"/>
+      <c r="H27" s="35" t="n"/>
+      <c r="I27" s="35" t="n"/>
+      <c r="J27" s="35" t="n"/>
+      <c r="K27" s="35" t="n"/>
+      <c r="L27" s="36" t="n"/>
+      <c r="M27" s="44" t="n"/>
+      <c r="N27" s="44" t="n"/>
+      <c r="O27" s="45" t="n"/>
+    </row>
+    <row r="28" ht="25" customHeight="1" s="1">
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="35" t="n"/>
+      <c r="H28" s="35" t="n"/>
+      <c r="I28" s="35" t="n"/>
+      <c r="J28" s="35" t="n"/>
+      <c r="K28" s="35" t="n"/>
+      <c r="L28" s="36" t="n"/>
+      <c r="M28" s="44" t="n"/>
+      <c r="N28" s="44" t="n"/>
+      <c r="O28" s="45" t="n"/>
+    </row>
+    <row r="29" ht="25" customHeight="1" s="1">
+      <c r="A29" s="35" t="n"/>
+      <c r="B29" s="36" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="35" t="n"/>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="35" t="n"/>
+      <c r="G29" s="35" t="n"/>
+      <c r="H29" s="35" t="n"/>
+      <c r="I29" s="35" t="n"/>
+      <c r="J29" s="35" t="n"/>
+      <c r="K29" s="35" t="n"/>
+      <c r="L29" s="36" t="n"/>
+      <c r="M29" s="44" t="n"/>
+      <c r="N29" s="44" t="n"/>
+      <c r="O29" s="45" t="n"/>
+    </row>
+    <row r="30" ht="25" customHeight="1" s="1">
+      <c r="A30" s="35" t="n"/>
+      <c r="B30" s="36" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="35" t="n"/>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="35" t="n"/>
+      <c r="G30" s="35" t="n"/>
+      <c r="H30" s="35" t="n"/>
+      <c r="I30" s="35" t="n"/>
+      <c r="J30" s="35" t="n"/>
+      <c r="K30" s="35" t="n"/>
+      <c r="L30" s="36" t="n"/>
+      <c r="M30" s="44" t="n"/>
+      <c r="N30" s="44" t="n"/>
+      <c r="O30" s="45" t="n"/>
+    </row>
+    <row r="31" ht="25" customFormat="1" customHeight="1" s="17">
+      <c r="A31" s="35" t="n"/>
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="35" t="n"/>
+      <c r="E31" s="35" t="n"/>
+      <c r="F31" s="35" t="n"/>
+      <c r="G31" s="35" t="n"/>
+      <c r="H31" s="35" t="n"/>
+      <c r="I31" s="35" t="n"/>
+      <c r="J31" s="35" t="n"/>
+      <c r="K31" s="35" t="n"/>
+      <c r="L31" s="36" t="n"/>
+      <c r="M31" s="44" t="n"/>
+      <c r="N31" s="44" t="n"/>
+      <c r="O31" s="45" t="n"/>
+    </row>
+    <row r="32" ht="25" customFormat="1" customHeight="1" s="17">
+      <c r="A32" s="35" t="n"/>
+      <c r="B32" s="36" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="35" t="n"/>
+      <c r="E32" s="35" t="n"/>
+      <c r="F32" s="35" t="n"/>
+      <c r="G32" s="35" t="n"/>
+      <c r="H32" s="35" t="n"/>
+      <c r="I32" s="35" t="n"/>
+      <c r="J32" s="35" t="n"/>
+      <c r="K32" s="35" t="n"/>
+      <c r="L32" s="36" t="n"/>
+      <c r="M32" s="44" t="n"/>
+      <c r="N32" s="44" t="n"/>
+      <c r="O32" s="45" t="n"/>
+    </row>
+    <row r="33" ht="25" customHeight="1" s="1">
+      <c r="A33" s="35" t="n"/>
+      <c r="B33" s="36" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="35" t="n"/>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="35" t="n"/>
+      <c r="G33" s="35" t="n"/>
+      <c r="H33" s="35" t="n"/>
+      <c r="I33" s="35" t="n"/>
+      <c r="J33" s="35" t="n"/>
+      <c r="K33" s="35" t="n"/>
+      <c r="L33" s="36" t="n"/>
+      <c r="M33" s="44" t="n"/>
+      <c r="N33" s="44" t="n"/>
+      <c r="O33" s="45" t="n"/>
+    </row>
+    <row r="34" ht="25" customHeight="1" s="1">
+      <c r="A34" s="35" t="n"/>
+      <c r="B34" s="36" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="35" t="n"/>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="35" t="n"/>
+      <c r="G34" s="35" t="n"/>
+      <c r="H34" s="35" t="n"/>
+      <c r="I34" s="35" t="n"/>
+      <c r="J34" s="35" t="n"/>
+      <c r="K34" s="35" t="n"/>
+      <c r="L34" s="36" t="n"/>
+      <c r="M34" s="44" t="n"/>
+      <c r="N34" s="44" t="n"/>
+      <c r="O34" s="45" t="n"/>
+    </row>
+    <row r="35" ht="25" customHeight="1" s="1">
+      <c r="A35" s="35" t="n"/>
+      <c r="B35" s="36" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="35" t="n"/>
+      <c r="E35" s="35" t="n"/>
+      <c r="F35" s="35" t="n"/>
+      <c r="G35" s="35" t="n"/>
+      <c r="H35" s="35" t="n"/>
+      <c r="I35" s="35" t="n"/>
+      <c r="J35" s="35" t="n"/>
+      <c r="K35" s="35" t="n"/>
+      <c r="L35" s="36" t="n"/>
+      <c r="M35" s="44" t="n"/>
+      <c r="N35" s="44" t="n"/>
+      <c r="O35" s="45" t="n"/>
+    </row>
+    <row r="36" ht="25" customHeight="1" s="1">
+      <c r="A36" s="46" t="inlineStr">
         <is>
           <t>包装袋图片</t>
         </is>
       </c>
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B36" s="46" t="inlineStr">
         <is>
           <t>大货生产注意事项</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="56" t="inlineStr">
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="46" t="inlineStr">
         <is>
           <t>生产常规要求</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="4" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1" s="83">
-      <c r="A25" s="60" t="n"/>
-      <c r="B25" s="61" t="n"/>
-      <c r="C25" s="62" t="n"/>
-      <c r="D25" s="62" t="n"/>
-      <c r="E25" s="62" t="n"/>
-      <c r="F25" s="63" t="n"/>
-      <c r="G25" s="95" t="inlineStr">
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="35.1" customHeight="1" s="1">
+      <c r="A37" s="47" t="n"/>
+      <c r="B37" s="48" t="n"/>
+      <c r="C37" s="49" t="n"/>
+      <c r="D37" s="49" t="n"/>
+      <c r="E37" s="49" t="n"/>
+      <c r="F37" s="50" t="n"/>
+      <c r="G37" s="51" t="inlineStr">
         <is>
           <t>一、制作要求：
 1.衣服上不能有抽纱现象，污点要清洗干净
@@ -2549,155 +2647,155 @@
 4.单色齐码捆绑后装箱</t>
         </is>
       </c>
-      <c r="H25" s="62" t="n"/>
-      <c r="I25" s="62" t="n"/>
-      <c r="J25" s="62" t="n"/>
-      <c r="K25" s="62" t="n"/>
-      <c r="L25" s="62" t="n"/>
-      <c r="M25" s="62" t="n"/>
-      <c r="N25" s="62" t="n"/>
-      <c r="O25" s="63" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1" s="83">
-      <c r="A26" s="68" t="n"/>
-      <c r="B26" s="69" t="n"/>
-      <c r="F26" s="71" t="n"/>
-      <c r="G26" s="69" t="n"/>
-      <c r="O26" s="71" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1" s="83">
-      <c r="A27" s="68" t="n"/>
-      <c r="B27" s="69" t="n"/>
-      <c r="F27" s="71" t="n"/>
-      <c r="G27" s="69" t="n"/>
-      <c r="O27" s="71" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1" s="83">
-      <c r="A28" s="68" t="n"/>
-      <c r="B28" s="69" t="n"/>
-      <c r="F28" s="71" t="n"/>
-      <c r="G28" s="69" t="n"/>
-      <c r="O28" s="71" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1" s="83">
-      <c r="A29" s="68" t="n"/>
-      <c r="B29" s="69" t="n"/>
-      <c r="F29" s="71" t="n"/>
-      <c r="G29" s="69" t="n"/>
-      <c r="O29" s="71" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1" s="83">
-      <c r="A30" s="97" t="n"/>
-      <c r="B30" s="88" t="n"/>
-      <c r="C30" s="89" t="n"/>
-      <c r="D30" s="89" t="n"/>
-      <c r="E30" s="89" t="n"/>
-      <c r="F30" s="90" t="n"/>
-      <c r="G30" s="88" t="n"/>
-      <c r="H30" s="89" t="n"/>
-      <c r="I30" s="89" t="n"/>
-      <c r="J30" s="89" t="n"/>
-      <c r="K30" s="89" t="n"/>
-      <c r="L30" s="89" t="n"/>
-      <c r="M30" s="89" t="n"/>
-      <c r="N30" s="89" t="n"/>
-      <c r="O30" s="90" t="n"/>
-    </row>
-    <row r="31" ht="30" customFormat="1" customHeight="1" s="17">
-      <c r="A31" s="73" t="inlineStr">
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="49" t="n"/>
+      <c r="J37" s="49" t="n"/>
+      <c r="K37" s="49" t="n"/>
+      <c r="L37" s="49" t="n"/>
+      <c r="M37" s="49" t="n"/>
+      <c r="N37" s="49" t="n"/>
+      <c r="O37" s="50" t="n"/>
+    </row>
+    <row r="38" ht="35.1" customHeight="1" s="1">
+      <c r="A38" s="52" t="n"/>
+      <c r="B38" s="53" t="n"/>
+      <c r="F38" s="54" t="n"/>
+      <c r="G38" s="53" t="n"/>
+      <c r="O38" s="54" t="n"/>
+    </row>
+    <row r="39" ht="35.1" customHeight="1" s="1">
+      <c r="A39" s="52" t="n"/>
+      <c r="B39" s="53" t="n"/>
+      <c r="F39" s="54" t="n"/>
+      <c r="G39" s="53" t="n"/>
+      <c r="O39" s="54" t="n"/>
+    </row>
+    <row r="40" ht="35.1" customHeight="1" s="1">
+      <c r="A40" s="52" t="n"/>
+      <c r="B40" s="53" t="n"/>
+      <c r="F40" s="54" t="n"/>
+      <c r="G40" s="53" t="n"/>
+      <c r="O40" s="54" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1" s="1">
+      <c r="A41" s="52" t="n"/>
+      <c r="B41" s="53" t="n"/>
+      <c r="F41" s="54" t="n"/>
+      <c r="G41" s="53" t="n"/>
+      <c r="O41" s="54" t="n"/>
+    </row>
+    <row r="42" ht="31" customHeight="1" s="1">
+      <c r="A42" s="34" t="n"/>
+      <c r="B42" s="55" t="n"/>
+      <c r="C42" s="56" t="n"/>
+      <c r="D42" s="56" t="n"/>
+      <c r="E42" s="56" t="n"/>
+      <c r="F42" s="57" t="n"/>
+      <c r="G42" s="55" t="n"/>
+      <c r="H42" s="56" t="n"/>
+      <c r="I42" s="56" t="n"/>
+      <c r="J42" s="56" t="n"/>
+      <c r="K42" s="56" t="n"/>
+      <c r="L42" s="56" t="n"/>
+      <c r="M42" s="56" t="n"/>
+      <c r="N42" s="56" t="n"/>
+      <c r="O42" s="57" t="n"/>
+    </row>
+    <row r="43" ht="25" customHeight="1" s="1">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>来货验收质检流程：所有来货全检</t>
         </is>
       </c>
-      <c r="B31" s="62" t="n"/>
-      <c r="C31" s="62" t="n"/>
-      <c r="D31" s="62" t="n"/>
-      <c r="E31" s="62" t="n"/>
-      <c r="F31" s="62" t="n"/>
-      <c r="G31" s="62" t="n"/>
-      <c r="H31" s="62" t="n"/>
-      <c r="I31" s="62" t="n"/>
-      <c r="J31" s="62" t="n"/>
-      <c r="K31" s="62" t="n"/>
-      <c r="L31" s="62" t="n"/>
-      <c r="M31" s="62" t="n"/>
-      <c r="N31" s="62" t="n"/>
-      <c r="O31" s="63" t="n"/>
-    </row>
-    <row r="32" ht="30" customFormat="1" customHeight="1" s="17">
-      <c r="A32" s="88" t="n"/>
-      <c r="B32" s="89" t="n"/>
-      <c r="C32" s="89" t="n"/>
-      <c r="D32" s="89" t="n"/>
-      <c r="E32" s="89" t="n"/>
-      <c r="F32" s="89" t="n"/>
-      <c r="G32" s="89" t="n"/>
-      <c r="H32" s="89" t="n"/>
-      <c r="I32" s="89" t="n"/>
-      <c r="J32" s="89" t="n"/>
-      <c r="K32" s="89" t="n"/>
-      <c r="L32" s="89" t="n"/>
-      <c r="M32" s="89" t="n"/>
-      <c r="N32" s="89" t="n"/>
-      <c r="O32" s="90" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1" s="83">
-      <c r="A33" s="73" t="inlineStr">
+      <c r="B43" s="49" t="n"/>
+      <c r="C43" s="49" t="n"/>
+      <c r="D43" s="49" t="n"/>
+      <c r="E43" s="49" t="n"/>
+      <c r="F43" s="49" t="n"/>
+      <c r="G43" s="49" t="n"/>
+      <c r="H43" s="49" t="n"/>
+      <c r="I43" s="49" t="n"/>
+      <c r="J43" s="49" t="n"/>
+      <c r="K43" s="49" t="n"/>
+      <c r="L43" s="49" t="n"/>
+      <c r="M43" s="49" t="n"/>
+      <c r="N43" s="49" t="n"/>
+      <c r="O43" s="50" t="n"/>
+    </row>
+    <row r="44" ht="25" customHeight="1" s="1">
+      <c r="A44" s="55" t="n"/>
+      <c r="B44" s="56" t="n"/>
+      <c r="C44" s="56" t="n"/>
+      <c r="D44" s="56" t="n"/>
+      <c r="E44" s="56" t="n"/>
+      <c r="F44" s="56" t="n"/>
+      <c r="G44" s="56" t="n"/>
+      <c r="H44" s="56" t="n"/>
+      <c r="I44" s="56" t="n"/>
+      <c r="J44" s="56" t="n"/>
+      <c r="K44" s="56" t="n"/>
+      <c r="L44" s="56" t="n"/>
+      <c r="M44" s="56" t="n"/>
+      <c r="N44" s="56" t="n"/>
+      <c r="O44" s="57" t="n"/>
+    </row>
+    <row r="45" ht="36" customHeight="1" s="1">
+      <c r="A45" s="58" t="inlineStr">
         <is>
           <t>包装要求</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="25" customHeight="1" s="83">
-      <c r="A34" s="74" t="inlineStr">
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="49" t="n"/>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="49" t="n"/>
+      <c r="F45" s="49" t="n"/>
+      <c r="G45" s="49" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
+      <c r="J45" s="49" t="n"/>
+      <c r="K45" s="49" t="n"/>
+      <c r="L45" s="49" t="n"/>
+      <c r="M45" s="49" t="n"/>
+      <c r="N45" s="49" t="n"/>
+      <c r="O45" s="50" t="n"/>
+    </row>
+    <row r="46" ht="25" customHeight="1" s="1">
+      <c r="A46" s="59" t="inlineStr">
         <is>
           <t>主唛</t>
         </is>
       </c>
-      <c r="B34" s="89" t="n"/>
-      <c r="C34" s="90" t="n"/>
-      <c r="D34" s="77" t="inlineStr">
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="59" t="inlineStr">
         <is>
           <t>吊牌</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="80" t="inlineStr">
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="61" t="inlineStr">
         <is>
           <t>外包装袋贴纸内容</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="51.75" customHeight="1" s="83">
-      <c r="A35" s="81" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="82" t="n"/>
-      <c r="H35" s="71" t="n"/>
-      <c r="I35" s="85" t="inlineStr">
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="115" customHeight="1" s="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="63" t="n"/>
+      <c r="H47" s="54" t="n"/>
+      <c r="I47" s="64" t="inlineStr">
         <is>
           <t>款号-颜色-尺码
 名称
@@ -2705,100 +2803,100 @@
 -黑色-S</t>
         </is>
       </c>
-      <c r="J35" s="62" t="n"/>
-      <c r="K35" s="62" t="n"/>
-      <c r="L35" s="62" t="n"/>
-      <c r="M35" s="62" t="n"/>
-      <c r="N35" s="62" t="n"/>
-      <c r="O35" s="63" t="n"/>
-    </row>
-    <row r="36" ht="25" customHeight="1" s="83">
-      <c r="A36" s="86" t="inlineStr">
+      <c r="J47" s="49" t="n"/>
+      <c r="K47" s="49" t="n"/>
+      <c r="L47" s="49" t="n"/>
+      <c r="M47" s="49" t="n"/>
+      <c r="N47" s="49" t="n"/>
+      <c r="O47" s="50" t="n"/>
+    </row>
+    <row r="48" ht="25" customHeight="1" s="1">
+      <c r="A48" s="65" t="inlineStr">
         <is>
           <t>洗水唛内容</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="69" t="n"/>
-      <c r="H36" s="71" t="n"/>
-      <c r="I36" s="69" t="n"/>
-      <c r="O36" s="71" t="n"/>
-    </row>
-    <row r="37" ht="35.1" customHeight="1" s="83">
-      <c r="A37" s="87" t="inlineStr">
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="53" t="n"/>
+      <c r="H48" s="54" t="n"/>
+      <c r="I48" s="53" t="n"/>
+      <c r="O48" s="54" t="n"/>
+    </row>
+    <row r="49" ht="80" customHeight="1" s="1">
+      <c r="A49" s="66" t="inlineStr">
         <is>
           <t>95% Rayon, 5% Spandex</t>
         </is>
       </c>
-      <c r="B37" s="62" t="n"/>
-      <c r="C37" s="63" t="n"/>
-      <c r="D37" s="69" t="n"/>
-      <c r="H37" s="71" t="n"/>
-      <c r="I37" s="69" t="n"/>
-      <c r="O37" s="71" t="n"/>
-    </row>
-    <row r="38" ht="35.1" customHeight="1" s="83">
-      <c r="A38" s="69" t="n"/>
-      <c r="C38" s="71" t="n"/>
-      <c r="D38" s="69" t="n"/>
-      <c r="H38" s="71" t="n"/>
-      <c r="I38" s="69" t="n"/>
-      <c r="O38" s="71" t="n"/>
-    </row>
-    <row r="39" ht="35.1" customHeight="1" s="83">
-      <c r="A39" s="69" t="n"/>
-      <c r="C39" s="71" t="n"/>
-      <c r="D39" s="69" t="n"/>
-      <c r="H39" s="71" t="n"/>
-      <c r="I39" s="69" t="n"/>
-      <c r="O39" s="71" t="n"/>
-    </row>
-    <row r="40" ht="35.1" customHeight="1" s="83">
-      <c r="A40" s="88" t="n"/>
-      <c r="B40" s="89" t="n"/>
-      <c r="C40" s="90" t="n"/>
-      <c r="D40" s="88" t="n"/>
-      <c r="E40" s="89" t="n"/>
-      <c r="F40" s="89" t="n"/>
-      <c r="G40" s="89" t="n"/>
-      <c r="H40" s="90" t="n"/>
-      <c r="I40" s="88" t="n"/>
-      <c r="J40" s="89" t="n"/>
-      <c r="K40" s="89" t="n"/>
-      <c r="L40" s="89" t="n"/>
-      <c r="M40" s="89" t="n"/>
-      <c r="N40" s="89" t="n"/>
-      <c r="O40" s="90" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1" s="83">
-      <c r="A41" s="73" t="inlineStr">
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="50" t="n"/>
+      <c r="D49" s="53" t="n"/>
+      <c r="H49" s="54" t="n"/>
+      <c r="I49" s="53" t="n"/>
+      <c r="O49" s="54" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="53" t="n"/>
+      <c r="C50" s="54" t="n"/>
+      <c r="D50" s="53" t="n"/>
+      <c r="H50" s="54" t="n"/>
+      <c r="I50" s="53" t="n"/>
+      <c r="O50" s="54" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="53" t="n"/>
+      <c r="C51" s="54" t="n"/>
+      <c r="D51" s="53" t="n"/>
+      <c r="H51" s="54" t="n"/>
+      <c r="I51" s="53" t="n"/>
+      <c r="O51" s="54" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="55" t="n"/>
+      <c r="B52" s="56" t="n"/>
+      <c r="C52" s="57" t="n"/>
+      <c r="D52" s="55" t="n"/>
+      <c r="E52" s="56" t="n"/>
+      <c r="F52" s="56" t="n"/>
+      <c r="G52" s="56" t="n"/>
+      <c r="H52" s="57" t="n"/>
+      <c r="I52" s="55" t="n"/>
+      <c r="J52" s="56" t="n"/>
+      <c r="K52" s="56" t="n"/>
+      <c r="L52" s="56" t="n"/>
+      <c r="M52" s="56" t="n"/>
+      <c r="N52" s="56" t="n"/>
+      <c r="O52" s="57" t="n"/>
+    </row>
+    <row r="53" ht="31.5" customHeight="1" s="1">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>质检内容</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="4" t="n"/>
-    </row>
-    <row r="42" ht="25" customHeight="1" s="83">
-      <c r="A42" s="94" t="inlineStr">
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="n"/>
+      <c r="L53" s="3" t="n"/>
+      <c r="M53" s="3" t="n"/>
+      <c r="N53" s="3" t="n"/>
+      <c r="O53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="67" t="inlineStr">
         <is>
           <t>外观</t>
         </is>
       </c>
-      <c r="B42" s="95" t="inlineStr">
+      <c r="B54" s="51" t="inlineStr">
         <is>
           <t>1.无污渍、无明显异味
 2.无破损、口袋无破洞
@@ -2806,203 +2904,203 @@
 4.无明显色差</t>
         </is>
       </c>
-      <c r="C42" s="62" t="n"/>
-      <c r="D42" s="62" t="n"/>
-      <c r="E42" s="62" t="n"/>
-      <c r="F42" s="63" t="n"/>
-      <c r="G42" s="94" t="inlineStr">
+      <c r="C54" s="49" t="n"/>
+      <c r="D54" s="49" t="n"/>
+      <c r="E54" s="49" t="n"/>
+      <c r="F54" s="50" t="n"/>
+      <c r="G54" s="67" t="inlineStr">
         <is>
           <t>做工</t>
         </is>
       </c>
-      <c r="H42" s="62" t="n"/>
-      <c r="I42" s="62" t="n"/>
-      <c r="J42" s="62" t="n"/>
-      <c r="K42" s="63" t="n"/>
-      <c r="L42" s="95" t="inlineStr">
+      <c r="H54" s="49" t="n"/>
+      <c r="I54" s="49" t="n"/>
+      <c r="J54" s="49" t="n"/>
+      <c r="K54" s="50" t="n"/>
+      <c r="L54" s="51" t="inlineStr">
         <is>
           <t>1.无明显线头
 2.车线平顺</t>
         </is>
       </c>
-      <c r="M42" s="62" t="n"/>
-      <c r="N42" s="62" t="n"/>
-      <c r="O42" s="63" t="n"/>
-    </row>
-    <row r="43" ht="25" customHeight="1" s="83">
-      <c r="A43" s="68" t="n"/>
-      <c r="B43" s="69" t="n"/>
-      <c r="F43" s="71" t="n"/>
-      <c r="G43" s="69" t="n"/>
-      <c r="K43" s="71" t="n"/>
-      <c r="L43" s="69" t="n"/>
-      <c r="O43" s="71" t="n"/>
-    </row>
-    <row r="44" ht="25" customHeight="1" s="83">
-      <c r="A44" s="68" t="n"/>
-      <c r="B44" s="69" t="n"/>
-      <c r="F44" s="71" t="n"/>
-      <c r="G44" s="69" t="n"/>
-      <c r="K44" s="71" t="n"/>
-      <c r="L44" s="69" t="n"/>
-      <c r="O44" s="71" t="n"/>
-    </row>
-    <row r="45" ht="17" customHeight="1" s="83">
-      <c r="A45" s="97" t="n"/>
-      <c r="B45" s="88" t="n"/>
-      <c r="C45" s="89" t="n"/>
-      <c r="D45" s="89" t="n"/>
-      <c r="E45" s="89" t="n"/>
-      <c r="F45" s="90" t="n"/>
-      <c r="G45" s="88" t="n"/>
-      <c r="H45" s="89" t="n"/>
-      <c r="I45" s="89" t="n"/>
-      <c r="J45" s="89" t="n"/>
-      <c r="K45" s="90" t="n"/>
-      <c r="L45" s="88" t="n"/>
-      <c r="M45" s="89" t="n"/>
-      <c r="N45" s="89" t="n"/>
-      <c r="O45" s="90" t="n"/>
-    </row>
-    <row r="46" ht="25" customHeight="1" s="83">
-      <c r="A46" s="94" t="inlineStr">
+      <c r="M54" s="49" t="n"/>
+      <c r="N54" s="49" t="n"/>
+      <c r="O54" s="50" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="52" t="n"/>
+      <c r="B55" s="53" t="n"/>
+      <c r="F55" s="54" t="n"/>
+      <c r="G55" s="53" t="n"/>
+      <c r="K55" s="54" t="n"/>
+      <c r="L55" s="53" t="n"/>
+      <c r="O55" s="54" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="52" t="n"/>
+      <c r="B56" s="53" t="n"/>
+      <c r="F56" s="54" t="n"/>
+      <c r="G56" s="53" t="n"/>
+      <c r="K56" s="54" t="n"/>
+      <c r="L56" s="53" t="n"/>
+      <c r="O56" s="54" t="n"/>
+    </row>
+    <row r="57" ht="59" customHeight="1" s="1">
+      <c r="A57" s="34" t="n"/>
+      <c r="B57" s="55" t="n"/>
+      <c r="C57" s="56" t="n"/>
+      <c r="D57" s="56" t="n"/>
+      <c r="E57" s="56" t="n"/>
+      <c r="F57" s="57" t="n"/>
+      <c r="G57" s="55" t="n"/>
+      <c r="H57" s="56" t="n"/>
+      <c r="I57" s="56" t="n"/>
+      <c r="J57" s="56" t="n"/>
+      <c r="K57" s="57" t="n"/>
+      <c r="L57" s="55" t="n"/>
+      <c r="M57" s="56" t="n"/>
+      <c r="N57" s="56" t="n"/>
+      <c r="O57" s="57" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="67" t="inlineStr">
         <is>
           <t>包装</t>
         </is>
       </c>
-      <c r="B46" s="95" t="inlineStr">
+      <c r="B58" s="51" t="inlineStr">
         <is>
           <t>1.吊牌、包装与订单要求一致
 2.无不同码、不同色或者不同款混捆
 3.无串码、无款号贴错</t>
         </is>
       </c>
-      <c r="C46" s="62" t="n"/>
-      <c r="D46" s="62" t="n"/>
-      <c r="E46" s="62" t="n"/>
-      <c r="F46" s="63" t="n"/>
-      <c r="G46" s="94" t="inlineStr">
+      <c r="C58" s="49" t="n"/>
+      <c r="D58" s="49" t="n"/>
+      <c r="E58" s="49" t="n"/>
+      <c r="F58" s="50" t="n"/>
+      <c r="G58" s="67" t="inlineStr">
         <is>
           <t>尺寸</t>
         </is>
       </c>
-      <c r="H46" s="62" t="n"/>
-      <c r="I46" s="62" t="n"/>
-      <c r="J46" s="62" t="n"/>
-      <c r="K46" s="63" t="n"/>
-      <c r="L46" s="96" t="inlineStr">
+      <c r="H58" s="49" t="n"/>
+      <c r="I58" s="49" t="n"/>
+      <c r="J58" s="49" t="n"/>
+      <c r="K58" s="50" t="n"/>
+      <c r="L58" s="68" t="inlineStr">
         <is>
           <t>参照验收尺寸表
 以尺寸不能大于1/3或1/3个码为验收标准</t>
         </is>
       </c>
-      <c r="M46" s="62" t="n"/>
-      <c r="N46" s="62" t="n"/>
-      <c r="O46" s="63" t="n"/>
-    </row>
-    <row r="47" ht="25" customHeight="1" s="83">
-      <c r="A47" s="68" t="n"/>
-      <c r="B47" s="69" t="n"/>
-      <c r="F47" s="71" t="n"/>
-      <c r="G47" s="69" t="n"/>
-      <c r="K47" s="71" t="n"/>
-      <c r="L47" s="69" t="n"/>
-      <c r="O47" s="71" t="n"/>
-    </row>
-    <row r="48" ht="25" customHeight="1" s="83">
-      <c r="A48" s="97" t="n"/>
-      <c r="B48" s="88" t="n"/>
-      <c r="C48" s="89" t="n"/>
-      <c r="D48" s="89" t="n"/>
-      <c r="E48" s="89" t="n"/>
-      <c r="F48" s="90" t="n"/>
-      <c r="G48" s="88" t="n"/>
-      <c r="H48" s="89" t="n"/>
-      <c r="I48" s="89" t="n"/>
-      <c r="J48" s="89" t="n"/>
-      <c r="K48" s="90" t="n"/>
-      <c r="L48" s="88" t="n"/>
-      <c r="M48" s="89" t="n"/>
-      <c r="N48" s="89" t="n"/>
-      <c r="O48" s="90" t="n"/>
-    </row>
-    <row r="49" ht="80" customHeight="1" s="83">
-      <c r="A49" s="94" t="inlineStr">
+      <c r="M58" s="49" t="n"/>
+      <c r="N58" s="49" t="n"/>
+      <c r="O58" s="50" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="52" t="n"/>
+      <c r="B59" s="53" t="n"/>
+      <c r="F59" s="54" t="n"/>
+      <c r="G59" s="53" t="n"/>
+      <c r="K59" s="54" t="n"/>
+      <c r="L59" s="53" t="n"/>
+      <c r="O59" s="54" t="n"/>
+    </row>
+    <row r="60" ht="78" customHeight="1" s="1">
+      <c r="A60" s="34" t="n"/>
+      <c r="B60" s="55" t="n"/>
+      <c r="C60" s="56" t="n"/>
+      <c r="D60" s="56" t="n"/>
+      <c r="E60" s="56" t="n"/>
+      <c r="F60" s="57" t="n"/>
+      <c r="G60" s="55" t="n"/>
+      <c r="H60" s="56" t="n"/>
+      <c r="I60" s="56" t="n"/>
+      <c r="J60" s="56" t="n"/>
+      <c r="K60" s="57" t="n"/>
+      <c r="L60" s="55" t="n"/>
+      <c r="M60" s="56" t="n"/>
+      <c r="N60" s="56" t="n"/>
+      <c r="O60" s="57" t="n"/>
+    </row>
+    <row r="61" ht="69" customHeight="1" s="1">
+      <c r="A61" s="67" t="inlineStr">
         <is>
           <t>白色底面料</t>
         </is>
       </c>
-      <c r="B49" s="95" t="inlineStr">
+      <c r="B61" s="51" t="inlineStr">
         <is>
           <t>每件包装内要放温馨提示卡片</t>
         </is>
       </c>
-      <c r="C49" s="95" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="94" t="inlineStr">
+      <c r="C61" s="51" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="67" t="inlineStr">
         <is>
           <t>特殊设计部位</t>
         </is>
       </c>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="4" t="n"/>
-      <c r="L49" s="96" t="n"/>
-      <c r="M49" s="3" t="n"/>
-      <c r="N49" s="3" t="n"/>
-      <c r="O49" s="4" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="68" t="n"/>
+      <c r="M61" s="3" t="n"/>
+      <c r="N61" s="3" t="n"/>
+      <c r="O61" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="51">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="G46:K48"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="H4:O4"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="A43:O44"/>
+    <mergeCell ref="G61:K61"/>
+    <mergeCell ref="A54:A57"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="L46:O48"/>
-    <mergeCell ref="L49:O49"/>
-    <mergeCell ref="G24:O24"/>
-    <mergeCell ref="G25:O30"/>
+    <mergeCell ref="B37:F42"/>
+    <mergeCell ref="D47:H52"/>
+    <mergeCell ref="L61:O61"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="C49:F49"/>
-    <mergeCell ref="A31:O32"/>
-    <mergeCell ref="B46:F48"/>
-    <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A25:A30"/>
-    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A49:C52"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="M6:M7"/>
+    <mergeCell ref="B58:F60"/>
     <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="L42:O45"/>
+    <mergeCell ref="G54:K57"/>
+    <mergeCell ref="I46:O46"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="G49:K49"/>
+    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="A53:O53"/>
+    <mergeCell ref="L54:O57"/>
     <mergeCell ref="H2:O2"/>
-    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="I47:O52"/>
+    <mergeCell ref="B54:F57"/>
     <mergeCell ref="L6:L7"/>
+    <mergeCell ref="G58:K60"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="G42:K45"/>
-    <mergeCell ref="D35:H40"/>
-    <mergeCell ref="A37:C40"/>
-    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="H3:O3"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F30"/>
+    <mergeCell ref="L58:O60"/>
+    <mergeCell ref="G37:O42"/>
+    <mergeCell ref="G36:O36"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="I35:O40"/>
+    <mergeCell ref="A45:O45"/>
     <mergeCell ref="K6:K7"/>
-    <mergeCell ref="B42:F45"/>
-    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="D6:D7"/>
